--- a/excel/Rontgen.xlsx
+++ b/excel/Rontgen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.08.08\Rontgen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Rontgen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA966AD-2023-4B74-B918-CE388506911F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAA9BC6-E89E-400E-A742-7C70E302A8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -445,18 +445,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -465,11 +453,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1554,43 +1554,43 @@
     <col min="8" max="9" width="12.7109375" customWidth="1"/>
     <col min="10" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="5.7109375" customWidth="1"/>
-    <col min="15" max="22" width="10.7109375" customWidth="1"/>
+    <col min="15" max="24" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="33" t="s">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="O1" s="25" t="s">
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="O1" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="29" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="31"/>
-      <c r="U1" s="29" t="s">
+      <c r="T1" s="27"/>
+      <c r="U1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="31"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="27"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -1698,13 +1698,13 @@
         <f>'Riverland III butai VI, Vilnius'!B12</f>
         <v>46339</v>
       </c>
-      <c r="I3" s="20" t="str">
+      <c r="I3" s="12" t="str">
         <f>'Riverland III butai VI, Vilnius'!R3</f>
         <v/>
       </c>
       <c r="J3" s="11">
         <f ca="1">'Riverland III butai VI, Vilnius'!B13</f>
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="K3" s="11" t="str">
         <f ca="1">'Riverland III butai VI, Vilnius'!S3</f>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>4.7000000000000455</v>
+        <v>6.5900000000000318</v>
       </c>
       <c r="S3" s="5">
         <f>SUM(L3:L200)</f>
@@ -1740,23 +1740,23 @@
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M200)</f>
-        <v>26.490000000000002</v>
+        <v>28.380000000000003</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>704.7</v>
+        <v>706.59</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>30.490000000000009</v>
+        <v>32.379999999999995</v>
       </c>
       <c r="W3" s="15">
         <f>(U3-O3)/O3</f>
-        <v>4.5223298378843396E-2</v>
+        <v>4.8026579255721499E-2</v>
       </c>
       <c r="X3" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>6.2502047419548026E-2</v>
+        <v>5.9494104981422422E-2</v>
       </c>
       <c r="AC3" s="5" t="str">
         <f ca="1">'Riverland III butai VI, Vilnius'!AA2</f>
@@ -1795,13 +1795,13 @@
         <f>'Panemunės apartamentai IX'!B12</f>
         <v>46335</v>
       </c>
-      <c r="I4" s="20" t="str">
+      <c r="I4" s="12" t="str">
         <f>'Panemunės apartamentai IX'!R3</f>
         <v/>
       </c>
       <c r="J4" s="11">
         <f ca="1">'Panemunės apartamentai IX'!B13</f>
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="K4" s="11" t="str">
         <f ca="1">'Panemunės apartamentai IX'!S3</f>
@@ -1852,7 +1852,7 @@
         <f>'Spanguolių takai XXXVIII, Riešė'!B12</f>
         <v>46304</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="12">
         <f>'Spanguolių takai XXXVIII, Riešė'!R3</f>
         <v>46252</v>
       </c>
@@ -1909,13 +1909,13 @@
         <f>'Pylimo g. 57 butai II, Vilnius'!B12</f>
         <v>46325</v>
       </c>
-      <c r="I6" s="20" t="str">
+      <c r="I6" s="12" t="str">
         <f>'Pylimo g. 57 butai II, Vilnius'!R3</f>
         <v/>
       </c>
       <c r="J6" s="11">
         <f ca="1">'Pylimo g. 57 butai II, Vilnius'!B13</f>
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="K6" s="11" t="str">
         <f ca="1">'Pylimo g. 57 butai II, Vilnius'!S3</f>
@@ -1966,7 +1966,7 @@
         <f>'ROOTHAUS I, Vilnius'!B12</f>
         <v>46342</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="12">
         <f>'ROOTHAUS I, Vilnius'!R3</f>
         <v>46212</v>
       </c>
@@ -2023,13 +2023,13 @@
         <f>'UAB "NT reikalas" projektai VI'!B12</f>
         <v>46399</v>
       </c>
-      <c r="I8" s="20" t="str">
+      <c r="I8" s="12" t="str">
         <f>'UAB "NT reikalas" projektai VI'!R3</f>
         <v/>
       </c>
       <c r="J8" s="11">
         <f ca="1">'UAB "NT reikalas" projektai VI'!B13</f>
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="K8" s="11" t="str">
         <f ca="1">'UAB "NT reikalas" projektai VI'!S3</f>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="M8" s="5">
         <f>'UAB "NT reikalas" projektai VI'!P3</f>
-        <v>3.5300000000000002</v>
+        <v>5.42</v>
       </c>
       <c r="AC8" s="5" t="str">
         <f ca="1">'UAB "NT reikalas" projektai VI'!AA2</f>
@@ -2080,13 +2080,13 @@
         <f>'Kaip Niujorke XXXVIII, Vilnius'!B12</f>
         <v>46412</v>
       </c>
-      <c r="I9" s="20" t="str">
+      <c r="I9" s="12" t="str">
         <f>'Kaip Niujorke XXXVIII, Vilnius'!R3</f>
         <v/>
       </c>
       <c r="J9" s="11">
         <f ca="1">'Kaip Niujorke XXXVIII, Vilnius'!B13</f>
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="K9" s="11" t="str">
         <f ca="1">'Kaip Niujorke XXXVIII, Vilnius'!S3</f>
@@ -2137,13 +2137,13 @@
         <f>'UAB „Dear Home" projektai XV'!B12</f>
         <v>46593</v>
       </c>
-      <c r="I10" s="20" t="str">
+      <c r="I10" s="12" t="str">
         <f>'UAB „Dear Home" projektai XV'!R3</f>
         <v/>
       </c>
       <c r="J10" s="11">
         <f ca="1">'UAB „Dear Home" projektai XV'!B13</f>
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="K10" s="11" t="str">
         <f ca="1">'UAB „Dear Home" projektai XV'!S3</f>
@@ -2194,13 +2194,13 @@
         <f>'Laikas mėtoms VII, Vilnius'!B12</f>
         <v>46587</v>
       </c>
-      <c r="I11" s="20" t="str">
+      <c r="I11" s="12" t="str">
         <f>'Laikas mėtoms VII, Vilnius'!R3</f>
         <v/>
       </c>
       <c r="J11" s="11">
         <f ca="1">'Laikas mėtoms VII, Vilnius'!B13</f>
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="K11" s="11" t="str">
         <f ca="1">'Laikas mėtoms VII, Vilnius'!S3</f>
@@ -2228,7 +2228,7 @@
       <c r="F12" s="15"/>
       <c r="G12" s="5"/>
       <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
+      <c r="I12" s="12"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="5"/>
@@ -2244,7 +2244,7 @@
       <c r="F13" s="15"/>
       <c r="G13" s="5"/>
       <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
+      <c r="I13" s="12"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
       <c r="L13" s="5"/>
@@ -2260,7 +2260,7 @@
       <c r="F14" s="15"/>
       <c r="G14" s="5"/>
       <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
+      <c r="I14" s="12"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="5"/>
@@ -2276,7 +2276,7 @@
       <c r="F15" s="15"/>
       <c r="G15" s="5"/>
       <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
+      <c r="I15" s="12"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="5"/>
@@ -2292,7 +2292,7 @@
       <c r="F16" s="15"/>
       <c r="G16" s="5"/>
       <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
+      <c r="I16" s="12"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
       <c r="L16" s="5"/>
@@ -2308,7 +2308,7 @@
       <c r="F17" s="15"/>
       <c r="G17" s="5"/>
       <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="5"/>
@@ -2324,7 +2324,7 @@
       <c r="F18" s="15"/>
       <c r="G18" s="5"/>
       <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
+      <c r="I18" s="12"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="5"/>
@@ -2340,7 +2340,7 @@
       <c r="F19" s="15"/>
       <c r="G19" s="5"/>
       <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
       <c r="L19" s="5"/>
@@ -2356,7 +2356,7 @@
       <c r="F20" s="15"/>
       <c r="G20" s="5"/>
       <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
+      <c r="I20" s="12"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="5"/>
@@ -2372,7 +2372,7 @@
       <c r="F21" s="15"/>
       <c r="G21" s="5"/>
       <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
+      <c r="I21" s="12"/>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
       <c r="L21" s="5"/>
@@ -2388,7 +2388,7 @@
       <c r="F22" s="15"/>
       <c r="G22" s="5"/>
       <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
+      <c r="I22" s="12"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="5"/>
@@ -2404,7 +2404,7 @@
       <c r="F23" s="15"/>
       <c r="G23" s="5"/>
       <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
+      <c r="I23" s="12"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
       <c r="L23" s="5"/>
@@ -2420,7 +2420,7 @@
       <c r="F24" s="15"/>
       <c r="G24" s="5"/>
       <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
+      <c r="I24" s="12"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
       <c r="L24" s="5"/>
@@ -2436,7 +2436,7 @@
       <c r="F25" s="15"/>
       <c r="G25" s="5"/>
       <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
+      <c r="I25" s="12"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
       <c r="L25" s="5"/>
@@ -2452,7 +2452,7 @@
       <c r="F26" s="15"/>
       <c r="G26" s="5"/>
       <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
+      <c r="I26" s="12"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="5"/>
@@ -2468,7 +2468,7 @@
       <c r="F27" s="15"/>
       <c r="G27" s="5"/>
       <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
+      <c r="I27" s="12"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
       <c r="L27" s="5"/>
@@ -2500,11 +2500,11 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C3" location="'Riverland III butai (6)'!A1" display="'Riverland III butai (6)'!A1" xr:uid="{4D570A1C-4B37-4100-B350-716432AD4918}"/>
-    <hyperlink ref="C4" location="'Panemunės apartamentai (9)'!A1" display="'Panemunės apartamentai (9)'!A1" xr:uid="{6036774D-9777-4AF7-83F7-56D558CBB834}"/>
+    <hyperlink ref="C3" location="'Riverland III butai VI, Vilnius'!A1" display="'Riverland III butai VI, Vilnius'!A1" xr:uid="{4D570A1C-4B37-4100-B350-716432AD4918}"/>
+    <hyperlink ref="C4" location="'Panemunės apartamentai IX'!A1" display="'Panemunės apartamentai IX'!A1" xr:uid="{6036774D-9777-4AF7-83F7-56D558CBB834}"/>
     <hyperlink ref="C5" location="'Spanguolių takai XXXVIII, Riešė'!A1" display="'Spanguolių takai XXXVIII, Riešė'!A1" xr:uid="{3B3D5039-CE6F-4660-9342-AD3DEC2102EE}"/>
-    <hyperlink ref="C6" location="'Pylimo g. 57 butai (2)'!A1" display="'Pylimo g. 57 butai (2)'!A1" xr:uid="{E7702D2C-76CD-4E0C-BFD5-0D530CFCB9A2}"/>
-    <hyperlink ref="C7" location="'ROOTHAUS (1)'!A1" display="'ROOTHAUS (1)'!A1" xr:uid="{791EC8ED-11BE-492B-B2EB-A5920ED9056D}"/>
+    <hyperlink ref="C6" location="'Pylimo g. 57 butai II, Vilnius'!A1" display="'Pylimo g. 57 butai II, Vilnius'!A1" xr:uid="{E7702D2C-76CD-4E0C-BFD5-0D530CFCB9A2}"/>
+    <hyperlink ref="C7" location="'ROOTHAUS I, Vilnius'!A1" display="'ROOTHAUS I, Vilnius'!A1" xr:uid="{791EC8ED-11BE-492B-B2EB-A5920ED9056D}"/>
     <hyperlink ref="C8" location="'UAB &quot;NT reikalas&quot; projektai VI'!A1" display="'UAB &quot;NT reikalas&quot; projektai VI'!A1" xr:uid="{2E431F7A-3C8E-4BEF-98A8-E19DC8DB4C11}"/>
     <hyperlink ref="C9" location="'Kaip Niujorke XXXVIII, Vilnius'!A1" display="'Kaip Niujorke XXXVIII, Vilnius'!A1" xr:uid="{004C2AB4-67B1-4B9A-8AFA-CFBE99194E84}"/>
     <hyperlink ref="C10" location="'UAB „Dear Home&quot; projektai XV'!A1" display="'UAB „Dear Home&quot; projektai XV'!A1" xr:uid="{923750F4-4706-4251-AEE3-F4E05423E875}"/>
@@ -2567,21 +2567,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="25" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="32" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -2638,9 +2638,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>45964</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="2"/>
@@ -3723,21 +3723,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="25" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="32" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -3794,9 +3794,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>45964</v>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="2"/>
@@ -5204,11 +5204,11 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="23">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="K200" s="24">
         <f>Overview!U3</f>
-        <v>704.7</v>
+        <v>706.59</v>
       </c>
     </row>
   </sheetData>
@@ -5266,21 +5266,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="25" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="32" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -5325,9 +5325,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>46217</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -6389,21 +6389,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="25" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="32" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -6448,9 +6448,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>46216</v>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -7505,21 +7505,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="25" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="32" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -7564,9 +7564,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>46185</v>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -8617,21 +8617,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="25" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="32" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -8688,9 +8688,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>46027</v>
@@ -8746,11 +8746,11 @@
       </c>
       <c r="O3" s="5">
         <f>F42</f>
-        <v>3.5300000000000002</v>
+        <v>5.42</v>
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>3.5300000000000002</v>
+        <v>5.42</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -8786,14 +8786,24 @@
       <c r="E4" s="5">
         <v>0</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="F4" s="5">
+        <v>1.89</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1.89</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <v>46294</v>
+      </c>
+      <c r="K4" s="11">
+        <f t="shared" si="0"/>
+        <v>-2</v>
       </c>
       <c r="Y4" s="12">
         <f t="shared" ref="Y4:Y41" si="1">J3</f>
@@ -8828,11 +8838,11 @@
       </c>
       <c r="Y5" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46294</v>
       </c>
       <c r="Z5" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
@@ -9038,7 +9048,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -9669,7 +9679,7 @@
       </c>
       <c r="F42" s="5">
         <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
-        <v>3.5300000000000002</v>
+        <v>5.42</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="3"/>
@@ -9677,7 +9687,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="3"/>
-        <v>3.5300000000000002</v>
+        <v>5.42</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="3"/>
@@ -9770,21 +9780,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="25" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="32" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -9841,9 +9851,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>45972</v>
@@ -10174,7 +10184,7 @@
       <c r="A12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="12">
         <v>46342</v>
       </c>
       <c r="D12" s="12"/>
@@ -10933,21 +10943,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="25" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="32" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -11004,9 +11014,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>45967</v>
@@ -11360,7 +11370,7 @@
       </c>
       <c r="B13" s="11">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="5"/>
@@ -12091,21 +12101,21 @@
       <c r="K1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="25" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="32" t="s">
         <v>40</v>
       </c>
       <c r="Y1" s="18" t="s">
@@ -12162,9 +12172,9 @@
       <c r="P2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
       <c r="Y2" s="12">
         <f>B3</f>
         <v>45965</v>
@@ -12537,7 +12547,7 @@
       <c r="A12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="12">
         <v>46304</v>
       </c>
       <c r="D12" s="12"/>
